--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,45 +884,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034383</v>
+        <v>129034372</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441603</v>
+        <v>441713</v>
       </c>
       <c r="R4" t="n">
-        <v>6780143</v>
+        <v>6780359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +966,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R5" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1078,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034347</v>
+        <v>129034383</v>
       </c>
       <c r="B6" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441619</v>
+        <v>441603</v>
       </c>
       <c r="R6" t="n">
-        <v>6780174</v>
+        <v>6780143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034372</v>
+        <v>129034390</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441713</v>
+        <v>441693</v>
       </c>
       <c r="R7" t="n">
-        <v>6780359</v>
+        <v>6780262</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,54 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034367</v>
+        <v>129034347</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441649</v>
+        <v>441619</v>
       </c>
       <c r="R8" t="n">
-        <v>6780285</v>
+        <v>6780174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,18 +1375,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2128,49 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>56913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R16" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,7 +2212,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2235,45 +2230,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B17" t="n">
-        <v>56913</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R17" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,6 +2318,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034373</v>
+        <v>129034352</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>56913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,43 +2639,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441691</v>
+        <v>441684</v>
       </c>
       <c r="R21" t="n">
-        <v>6780347</v>
+        <v>6780293</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2712,7 +2703,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2721,7 +2712,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2740,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034352</v>
+        <v>129034377</v>
       </c>
       <c r="B22" t="n">
-        <v>56913</v>
+        <v>57827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,34 +2741,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441684</v>
+        <v>441644</v>
       </c>
       <c r="R22" t="n">
-        <v>6780293</v>
+        <v>6780119</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034377</v>
+        <v>129034373</v>
       </c>
       <c r="B23" t="n">
-        <v>57827</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,31 +2851,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2885,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441644</v>
+        <v>441691</v>
       </c>
       <c r="R23" t="n">
-        <v>6780119</v>
+        <v>6780347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2924,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,45 +2952,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034376</v>
+        <v>129034375</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441689</v>
+        <v>441625</v>
       </c>
       <c r="R24" t="n">
-        <v>6780316</v>
+        <v>6780181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,6 +3032,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,7 +3064,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034375</v>
+        <v>129034364</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3094,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441625</v>
+        <v>441595</v>
       </c>
       <c r="R25" t="n">
-        <v>6780181</v>
+        <v>6780188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,54 +3176,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034364</v>
+        <v>129034376</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441595</v>
+        <v>441689</v>
       </c>
       <c r="R26" t="n">
-        <v>6780188</v>
+        <v>6780316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,11 +3247,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3371,45 +3371,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R28" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,12 +3453,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3468,45 +3483,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R29" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,7 +3567,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3552,6 +3576,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,54 +3595,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R30" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,18 +3668,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3682,54 +3692,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R31" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3767,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3775,7 +3776,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R2" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +757,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,54 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R3" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,54 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034372</v>
+        <v>129034347</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441713</v>
+        <v>441619</v>
       </c>
       <c r="R4" t="n">
-        <v>6780359</v>
+        <v>6780174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,18 +957,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034367</v>
+        <v>129034383</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441649</v>
+        <v>441603</v>
       </c>
       <c r="R5" t="n">
-        <v>6780285</v>
+        <v>6780143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034383</v>
+        <v>129034390</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441603</v>
+        <v>441693</v>
       </c>
       <c r="R6" t="n">
-        <v>6780143</v>
+        <v>6780262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,45 +1175,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R7" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1257,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,45 +1287,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B8" t="n">
-        <v>79066</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R8" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1369,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>129034382</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129034348</v>
       </c>
       <c r="B10" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129034386</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,45 +2128,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B16" t="n">
-        <v>56913</v>
+        <v>91546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R16" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,6 +2216,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2230,49 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>56913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R17" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,7 +2319,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>129034346</v>
       </c>
       <c r="B18" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129034387</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>129034397</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,54 +2952,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034375</v>
+        <v>129034376</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441625</v>
+        <v>441689</v>
       </c>
       <c r="R24" t="n">
-        <v>6780181</v>
+        <v>6780316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3064,7 +3050,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034364</v>
+        <v>129034375</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3108,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441595</v>
+        <v>441625</v>
       </c>
       <c r="R25" t="n">
-        <v>6780188</v>
+        <v>6780181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,45 +3162,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034376</v>
+        <v>129034364</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441689</v>
+        <v>441595</v>
       </c>
       <c r="R26" t="n">
-        <v>6780316</v>
+        <v>6780188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,6 +3242,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3277,7 +3277,7 @@
         <v>129034384</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,54 +3371,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R28" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,18 +3444,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3483,54 +3468,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R29" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,7 +3543,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,7 +3552,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3595,45 +3570,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R30" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,12 +3652,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3692,45 +3682,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R31" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,7 +3766,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3776,6 +3775,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R33" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R34" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4103,7 +4103,7 @@
         <v>129034389</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>129034395</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>129034388</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>129034396</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R2" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,18 +748,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R3" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034367</v>
+        <v>129034372</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441649</v>
+        <v>441713</v>
       </c>
       <c r="R7" t="n">
-        <v>6780285</v>
+        <v>6780359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034372</v>
+        <v>129034367</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441713</v>
+        <v>441649</v>
       </c>
       <c r="R8" t="n">
-        <v>6780359</v>
+        <v>6780285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,45 +1705,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034392</v>
+        <v>129034365</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441684</v>
+        <v>441629</v>
       </c>
       <c r="R12" t="n">
-        <v>6780236</v>
+        <v>6780255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034365</v>
+        <v>129034371</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441629</v>
+        <v>441664</v>
       </c>
       <c r="R13" t="n">
-        <v>6780255</v>
+        <v>6780325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,54 +1929,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034371</v>
+        <v>129034392</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441664</v>
+        <v>441684</v>
       </c>
       <c r="R14" t="n">
-        <v>6780325</v>
+        <v>6780236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034352</v>
+        <v>129034377</v>
       </c>
       <c r="B21" t="n">
-        <v>56913</v>
+        <v>57827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,34 +2639,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441684</v>
+        <v>441644</v>
       </c>
       <c r="R21" t="n">
-        <v>6780293</v>
+        <v>6780119</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034377</v>
+        <v>129034352</v>
       </c>
       <c r="B22" t="n">
-        <v>57827</v>
+        <v>56913</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,42 +2749,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441644</v>
+        <v>441684</v>
       </c>
       <c r="R22" t="n">
-        <v>6780119</v>
+        <v>6780293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R33" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R34" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R2" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +757,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,54 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R3" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1705,54 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034365</v>
+        <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441629</v>
+        <v>441684</v>
       </c>
       <c r="R12" t="n">
-        <v>6780255</v>
+        <v>6780236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1789,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034371</v>
+        <v>129034365</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441664</v>
+        <v>441629</v>
       </c>
       <c r="R13" t="n">
-        <v>6780325</v>
+        <v>6780255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,45 +1919,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034392</v>
+        <v>129034371</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441684</v>
+        <v>441664</v>
       </c>
       <c r="R14" t="n">
-        <v>6780236</v>
+        <v>6780325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,6 +2012,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -3371,45 +3371,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R28" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,12 +3453,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3468,45 +3483,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R29" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,7 +3567,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3552,6 +3576,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,54 +3595,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R30" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,18 +3668,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3682,54 +3692,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R31" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3767,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3775,7 +3776,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R33" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R34" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,45 +884,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B4" t="n">
-        <v>79067</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R4" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +966,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034383</v>
+        <v>129034367</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441603</v>
+        <v>441649</v>
       </c>
       <c r="R5" t="n">
-        <v>6780143</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1078,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034390</v>
+        <v>129034347</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441693</v>
+        <v>441619</v>
       </c>
       <c r="R6" t="n">
-        <v>6780262</v>
+        <v>6780174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034372</v>
+        <v>129034383</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441713</v>
+        <v>441603</v>
       </c>
       <c r="R7" t="n">
-        <v>6780359</v>
+        <v>6780143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,54 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R8" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,18 +1375,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2434,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034387</v>
+        <v>129034397</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441683</v>
+        <v>441616</v>
       </c>
       <c r="R19" t="n">
-        <v>6780346</v>
+        <v>6780103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034397</v>
+        <v>129034387</v>
       </c>
       <c r="B20" t="n">
         <v>79035</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441616</v>
+        <v>441683</v>
       </c>
       <c r="R20" t="n">
-        <v>6780103</v>
+        <v>6780346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034377</v>
+        <v>129034352</v>
       </c>
       <c r="B21" t="n">
-        <v>57827</v>
+        <v>56913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,42 +2639,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441644</v>
+        <v>441684</v>
       </c>
       <c r="R21" t="n">
-        <v>6780119</v>
+        <v>6780293</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2703,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034352</v>
+        <v>129034377</v>
       </c>
       <c r="B22" t="n">
-        <v>56913</v>
+        <v>57827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,34 +2741,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441684</v>
+        <v>441644</v>
       </c>
       <c r="R22" t="n">
-        <v>6780293</v>
+        <v>6780119</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,45 +2952,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034376</v>
+        <v>129034375</v>
       </c>
       <c r="B24" t="n">
-        <v>79071</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441689</v>
+        <v>441625</v>
       </c>
       <c r="R24" t="n">
-        <v>6780316</v>
+        <v>6780181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,6 +3032,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,7 +3064,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034375</v>
+        <v>129034364</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3094,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441625</v>
+        <v>441595</v>
       </c>
       <c r="R25" t="n">
-        <v>6780181</v>
+        <v>6780188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,54 +3176,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034364</v>
+        <v>129034376</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441595</v>
+        <v>441689</v>
       </c>
       <c r="R26" t="n">
-        <v>6780188</v>
+        <v>6780316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,11 +3247,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R2" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,18 +748,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R3" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,54 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034372</v>
+        <v>129034383</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441713</v>
+        <v>441603</v>
       </c>
       <c r="R4" t="n">
-        <v>6780359</v>
+        <v>6780143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,18 +957,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R5" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,45 +1078,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B6" t="n">
-        <v>79067</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R6" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1160,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,45 +1190,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034383</v>
+        <v>129034367</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441603</v>
+        <v>441649</v>
       </c>
       <c r="R7" t="n">
-        <v>6780143</v>
+        <v>6780285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1272,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034390</v>
+        <v>129034347</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441693</v>
+        <v>441619</v>
       </c>
       <c r="R8" t="n">
-        <v>6780262</v>
+        <v>6780174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
         <v>129034382</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129034348</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129034386</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,49 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B16" t="n">
-        <v>91546</v>
+        <v>56915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R16" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,7 +2212,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2235,45 +2230,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B17" t="n">
-        <v>56913</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R17" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,6 +2318,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>129034346</v>
       </c>
       <c r="B18" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034397</v>
+        <v>129034387</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441616</v>
+        <v>441683</v>
       </c>
       <c r="R19" t="n">
-        <v>6780103</v>
+        <v>6780346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034387</v>
+        <v>129034397</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441683</v>
+        <v>441616</v>
       </c>
       <c r="R20" t="n">
-        <v>6780346</v>
+        <v>6780103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>129034352</v>
       </c>
       <c r="B21" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034377</v>
+        <v>129034373</v>
       </c>
       <c r="B22" t="n">
-        <v>57827</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,31 +2741,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2773,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441644</v>
+        <v>441691</v>
       </c>
       <c r="R22" t="n">
-        <v>6780119</v>
+        <v>6780347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2814,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,6 +2823,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2840,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034373</v>
+        <v>129034377</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57829</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,32 +2853,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2884,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441691</v>
+        <v>441644</v>
       </c>
       <c r="R23" t="n">
-        <v>6780347</v>
+        <v>6780119</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2925,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,7 +2934,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,54 +2952,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034375</v>
+        <v>129034376</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441625</v>
+        <v>441689</v>
       </c>
       <c r="R24" t="n">
-        <v>6780181</v>
+        <v>6780316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3064,7 +3050,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034364</v>
+        <v>129034375</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3108,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441595</v>
+        <v>441625</v>
       </c>
       <c r="R25" t="n">
-        <v>6780188</v>
+        <v>6780181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,45 +3162,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034376</v>
+        <v>129034364</v>
       </c>
       <c r="B26" t="n">
-        <v>79071</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441689</v>
+        <v>441595</v>
       </c>
       <c r="R26" t="n">
-        <v>6780316</v>
+        <v>6780188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,6 +3242,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3277,7 +3277,7 @@
         <v>129034384</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,54 +3371,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R28" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,18 +3444,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3483,54 +3468,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R29" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,7 +3543,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,7 +3552,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3595,45 +3570,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R30" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,12 +3652,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3692,45 +3682,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R31" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,7 +3766,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3776,6 +3775,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R33" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R34" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4103,7 +4103,7 @@
         <v>129034389</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>129034395</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>129034388</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>129034349</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>129034396</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>129034353</v>
       </c>
       <c r="B40" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>129034363</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>129034361</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>129034358</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129034360</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>129034357</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>129034362</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034383</v>
+        <v>129034347</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441603</v>
+        <v>441619</v>
       </c>
       <c r="R4" t="n">
-        <v>6780143</v>
+        <v>6780174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,45 +981,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034390</v>
+        <v>129034372</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441693</v>
+        <v>441713</v>
       </c>
       <c r="R5" t="n">
-        <v>6780262</v>
+        <v>6780359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1063,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034372</v>
+        <v>129034367</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1122,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441713</v>
+        <v>441649</v>
       </c>
       <c r="R6" t="n">
-        <v>6780359</v>
+        <v>6780285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034367</v>
+        <v>129034383</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441649</v>
+        <v>441603</v>
       </c>
       <c r="R7" t="n">
-        <v>6780285</v>
+        <v>6780143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034347</v>
+        <v>129034390</v>
       </c>
       <c r="B8" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441619</v>
+        <v>441693</v>
       </c>
       <c r="R8" t="n">
-        <v>6780174</v>
+        <v>6780262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,45 +1705,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034392</v>
+        <v>129034365</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441684</v>
+        <v>441629</v>
       </c>
       <c r="R12" t="n">
-        <v>6780236</v>
+        <v>6780255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034365</v>
+        <v>129034371</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441629</v>
+        <v>441664</v>
       </c>
       <c r="R13" t="n">
-        <v>6780255</v>
+        <v>6780325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,54 +1929,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034371</v>
+        <v>129034392</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441664</v>
+        <v>441684</v>
       </c>
       <c r="R14" t="n">
-        <v>6780325</v>
+        <v>6780236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034373</v>
+        <v>129034377</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,32 +2741,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2774,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441691</v>
+        <v>441644</v>
       </c>
       <c r="R22" t="n">
-        <v>6780347</v>
+        <v>6780119</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,7 +2822,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2842,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034377</v>
+        <v>129034373</v>
       </c>
       <c r="B23" t="n">
-        <v>57829</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,31 +2851,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2885,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441644</v>
+        <v>441691</v>
       </c>
       <c r="R23" t="n">
-        <v>6780119</v>
+        <v>6780347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2924,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R33" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R34" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -981,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034372</v>
+        <v>129034390</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441713</v>
+        <v>441693</v>
       </c>
       <c r="R5" t="n">
-        <v>6780359</v>
+        <v>6780262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,54 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034367</v>
+        <v>129034383</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441649</v>
+        <v>441603</v>
       </c>
       <c r="R6" t="n">
-        <v>6780285</v>
+        <v>6780143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,18 +1151,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,45 +1175,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034383</v>
+        <v>129034372</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441603</v>
+        <v>441713</v>
       </c>
       <c r="R7" t="n">
-        <v>6780143</v>
+        <v>6780359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1257,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,45 +1287,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R8" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1369,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1705,54 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034365</v>
+        <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441629</v>
+        <v>441684</v>
       </c>
       <c r="R12" t="n">
-        <v>6780255</v>
+        <v>6780236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1789,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034371</v>
+        <v>129034365</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441664</v>
+        <v>441629</v>
       </c>
       <c r="R13" t="n">
-        <v>6780325</v>
+        <v>6780255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,45 +1919,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034392</v>
+        <v>129034371</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441684</v>
+        <v>441664</v>
       </c>
       <c r="R14" t="n">
-        <v>6780236</v>
+        <v>6780325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,6 +2012,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,45 +2128,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B16" t="n">
-        <v>56915</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R16" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,6 +2216,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2230,49 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>56915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R17" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,7 +2319,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2434,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034387</v>
+        <v>129034397</v>
       </c>
       <c r="B19" t="n">
         <v>79039</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441683</v>
+        <v>441616</v>
       </c>
       <c r="R19" t="n">
-        <v>6780346</v>
+        <v>6780103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034397</v>
+        <v>129034387</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441616</v>
+        <v>441683</v>
       </c>
       <c r="R20" t="n">
-        <v>6780103</v>
+        <v>6780346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034385</v>
+        <v>129034394</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441619</v>
+        <v>441672</v>
       </c>
       <c r="R28" t="n">
-        <v>6780221</v>
+        <v>6780172</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,6 +3442,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3468,7 +3473,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034394</v>
+        <v>129034385</v>
       </c>
       <c r="B29" t="n">
         <v>79039</v>
@@ -3503,10 +3508,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441672</v>
+        <v>441619</v>
       </c>
       <c r="R29" t="n">
-        <v>6780172</v>
+        <v>6780221</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,11 +3544,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034395</v>
+        <v>129034388</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441620</v>
+        <v>441700</v>
       </c>
       <c r="R36" t="n">
-        <v>6780175</v>
+        <v>6780320</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 30 m</t>
+          <t>Måttligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4299,7 +4299,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129034388</v>
+        <v>129034395</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441700</v>
+        <v>441620</v>
       </c>
       <c r="R37" t="n">
-        <v>6780320</v>
+        <v>6780175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie av 20 m</t>
+          <t>Rikligt i en radie om 30 m</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034393</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,45 +884,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B4" t="n">
-        <v>79071</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R4" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +966,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R5" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1078,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034383</v>
+        <v>129034347</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441603</v>
+        <v>441619</v>
       </c>
       <c r="R6" t="n">
-        <v>6780143</v>
+        <v>6780174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034372</v>
+        <v>129034383</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441713</v>
+        <v>441603</v>
       </c>
       <c r="R7" t="n">
-        <v>6780359</v>
+        <v>6780143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,54 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R8" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,18 +1375,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>129034382</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129034348</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,45 +1705,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034392</v>
+        <v>129034365</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441684</v>
+        <v>441629</v>
       </c>
       <c r="R12" t="n">
-        <v>6780236</v>
+        <v>6780255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034365</v>
+        <v>129034371</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441629</v>
+        <v>441664</v>
       </c>
       <c r="R13" t="n">
-        <v>6780255</v>
+        <v>6780325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,54 +1929,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034371</v>
+        <v>129034392</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441664</v>
+        <v>441684</v>
       </c>
       <c r="R14" t="n">
-        <v>6780325</v>
+        <v>6780236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>129034386</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129034355</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129034351</v>
       </c>
       <c r="B17" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129034346</v>
       </c>
       <c r="B18" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034397</v>
+        <v>129034387</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441616</v>
+        <v>441683</v>
       </c>
       <c r="R19" t="n">
-        <v>6780103</v>
+        <v>6780346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034387</v>
+        <v>129034397</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441683</v>
+        <v>441616</v>
       </c>
       <c r="R20" t="n">
-        <v>6780346</v>
+        <v>6780103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>129034352</v>
       </c>
       <c r="B21" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034377</v>
+        <v>129034373</v>
       </c>
       <c r="B22" t="n">
-        <v>57829</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,31 +2741,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2773,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441644</v>
+        <v>441691</v>
       </c>
       <c r="R22" t="n">
-        <v>6780119</v>
+        <v>6780347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2814,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,6 +2823,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2840,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034373</v>
+        <v>129034377</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,32 +2853,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2884,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441691</v>
+        <v>441644</v>
       </c>
       <c r="R23" t="n">
-        <v>6780347</v>
+        <v>6780119</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2925,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,7 +2934,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>129034376</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>129034384</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034394</v>
+        <v>129034385</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441672</v>
+        <v>441619</v>
       </c>
       <c r="R28" t="n">
-        <v>6780172</v>
+        <v>6780221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,11 +3442,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3473,10 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034385</v>
+        <v>129034394</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3508,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441619</v>
+        <v>441672</v>
       </c>
       <c r="R29" t="n">
-        <v>6780221</v>
+        <v>6780172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,6 +3539,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R33" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R34" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4103,7 +4103,7 @@
         <v>129034389</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034388</v>
+        <v>129034395</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441700</v>
+        <v>441620</v>
       </c>
       <c r="R36" t="n">
-        <v>6780320</v>
+        <v>6780175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie av 20 m</t>
+          <t>Rikligt i en radie om 30 m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129034395</v>
+        <v>129034388</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441620</v>
+        <v>441700</v>
       </c>
       <c r="R37" t="n">
-        <v>6780175</v>
+        <v>6780320</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 30 m</t>
+          <t>Måttligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4404,7 +4404,7 @@
         <v>129034349</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>129034396</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>129034353</v>
       </c>
       <c r="B40" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>129034363</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>129034361</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>129034358</v>
       </c>
       <c r="B43" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129034360</v>
       </c>
       <c r="B44" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>129034357</v>
       </c>
       <c r="B45" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>129034362</v>
       </c>
       <c r="B46" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,54 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034372</v>
+        <v>129034347</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441713</v>
+        <v>441619</v>
       </c>
       <c r="R4" t="n">
-        <v>6780359</v>
+        <v>6780174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,18 +957,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034367</v>
+        <v>129034383</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441649</v>
+        <v>441603</v>
       </c>
       <c r="R5" t="n">
-        <v>6780285</v>
+        <v>6780143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034347</v>
+        <v>129034390</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441619</v>
+        <v>441693</v>
       </c>
       <c r="R6" t="n">
-        <v>6780174</v>
+        <v>6780262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,45 +1175,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034383</v>
+        <v>129034372</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441603</v>
+        <v>441713</v>
       </c>
       <c r="R7" t="n">
-        <v>6780143</v>
+        <v>6780359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1257,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,45 +1287,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R8" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1369,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1705,54 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034365</v>
+        <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441629</v>
+        <v>441684</v>
       </c>
       <c r="R12" t="n">
-        <v>6780255</v>
+        <v>6780236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1789,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034371</v>
+        <v>129034365</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441664</v>
+        <v>441629</v>
       </c>
       <c r="R13" t="n">
-        <v>6780325</v>
+        <v>6780255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,45 +1919,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034392</v>
+        <v>129034371</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441684</v>
+        <v>441664</v>
       </c>
       <c r="R14" t="n">
-        <v>6780236</v>
+        <v>6780325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,6 +2012,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,49 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B16" t="n">
-        <v>91562</v>
+        <v>56917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R16" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,7 +2212,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2235,45 +2230,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B17" t="n">
-        <v>56917</v>
+        <v>91562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R17" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,6 +2318,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034373</v>
+        <v>129034377</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,32 +2741,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2774,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441691</v>
+        <v>441644</v>
       </c>
       <c r="R22" t="n">
-        <v>6780347</v>
+        <v>6780119</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,7 +2822,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2842,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034377</v>
+        <v>129034373</v>
       </c>
       <c r="B23" t="n">
-        <v>57831</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,31 +2851,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2885,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441644</v>
+        <v>441691</v>
       </c>
       <c r="R23" t="n">
-        <v>6780119</v>
+        <v>6780347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2924,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034385</v>
+        <v>129034394</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441619</v>
+        <v>441672</v>
       </c>
       <c r="R28" t="n">
-        <v>6780221</v>
+        <v>6780172</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,6 +3442,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3468,7 +3473,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034394</v>
+        <v>129034385</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3503,10 +3508,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441672</v>
+        <v>441619</v>
       </c>
       <c r="R29" t="n">
-        <v>6780172</v>
+        <v>6780221</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,11 +3544,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R33" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R34" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R2" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +757,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,54 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R3" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034395</v>
+        <v>129034349</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441620</v>
+        <v>441687</v>
       </c>
       <c r="R36" t="n">
-        <v>6780175</v>
+        <v>6780170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 30 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4401,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034349</v>
+        <v>129034395</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4412,21 +4412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441687</v>
+        <v>441620</v>
       </c>
       <c r="R38" t="n">
-        <v>6780170</v>
+        <v>6780175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 30 m</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,45 +884,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B4" t="n">
-        <v>79073</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R4" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +966,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034383</v>
+        <v>129034367</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441603</v>
+        <v>441649</v>
       </c>
       <c r="R5" t="n">
-        <v>6780143</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1078,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034390</v>
+        <v>129034347</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441693</v>
+        <v>441619</v>
       </c>
       <c r="R6" t="n">
-        <v>6780262</v>
+        <v>6780174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034372</v>
+        <v>129034383</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441713</v>
+        <v>441603</v>
       </c>
       <c r="R7" t="n">
-        <v>6780359</v>
+        <v>6780143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,54 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R8" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,18 +1375,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>129034355</v>
       </c>
       <c r="B17" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,45 +3371,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034394</v>
+        <v>129034374</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441672</v>
+        <v>441642</v>
       </c>
       <c r="R28" t="n">
-        <v>6780172</v>
+        <v>6780164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,7 +3455,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3455,6 +3464,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3473,45 +3483,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034385</v>
+        <v>129034368</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441619</v>
+        <v>441643</v>
       </c>
       <c r="R29" t="n">
-        <v>6780221</v>
+        <v>6780310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,12 +3565,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,54 +3595,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R30" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,18 +3668,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3682,54 +3692,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R31" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3767,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3775,7 +3776,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R33" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R34" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4197,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034349</v>
+        <v>129034395</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441687</v>
+        <v>441620</v>
       </c>
       <c r="R36" t="n">
-        <v>6780170</v>
+        <v>6780175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 30 m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4401,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034395</v>
+        <v>129034349</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4412,21 +4412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441620</v>
+        <v>441687</v>
       </c>
       <c r="R38" t="n">
-        <v>6780175</v>
+        <v>6780170</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 30 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034360</v>
+        <v>129034357</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441592</v>
+        <v>441595</v>
       </c>
       <c r="R44" t="n">
-        <v>6780185</v>
+        <v>6780107</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129034357</v>
+        <v>129034360</v>
       </c>
       <c r="B45" t="n">
         <v>57724</v>
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441595</v>
+        <v>441592</v>
       </c>
       <c r="R45" t="n">
-        <v>6780107</v>
+        <v>6780185</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,54 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034372</v>
+        <v>129034383</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441713</v>
+        <v>441603</v>
       </c>
       <c r="R4" t="n">
-        <v>6780359</v>
+        <v>6780143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,18 +957,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R5" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,45 +1078,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034347</v>
+        <v>129034372</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441619</v>
+        <v>441713</v>
       </c>
       <c r="R6" t="n">
-        <v>6780174</v>
+        <v>6780359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1160,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,45 +1190,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034383</v>
+        <v>129034367</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441603</v>
+        <v>441649</v>
       </c>
       <c r="R7" t="n">
-        <v>6780143</v>
+        <v>6780285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1272,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034390</v>
+        <v>129034347</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441693</v>
+        <v>441619</v>
       </c>
       <c r="R8" t="n">
-        <v>6780262</v>
+        <v>6780174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,45 +1705,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034392</v>
+        <v>129034365</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441684</v>
+        <v>441629</v>
       </c>
       <c r="R12" t="n">
-        <v>6780236</v>
+        <v>6780255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034365</v>
+        <v>129034371</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441629</v>
+        <v>441664</v>
       </c>
       <c r="R13" t="n">
-        <v>6780255</v>
+        <v>6780325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,54 +1929,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034371</v>
+        <v>129034392</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441664</v>
+        <v>441684</v>
       </c>
       <c r="R14" t="n">
-        <v>6780325</v>
+        <v>6780236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,45 +2128,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B16" t="n">
-        <v>56917</v>
+        <v>91561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R16" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,6 +2216,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2230,49 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>56917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R17" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,7 +2319,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034352</v>
+        <v>129034377</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>57831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,34 +2639,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441684</v>
+        <v>441644</v>
       </c>
       <c r="R21" t="n">
-        <v>6780293</v>
+        <v>6780119</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>3 individer</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034377</v>
+        <v>129034352</v>
       </c>
       <c r="B22" t="n">
-        <v>57831</v>
+        <v>56917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,42 +2749,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441644</v>
+        <v>441684</v>
       </c>
       <c r="R22" t="n">
-        <v>6780119</v>
+        <v>6780293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3 individer</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3371,54 +3371,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R28" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,18 +3444,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3483,54 +3468,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R29" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,7 +3543,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,7 +3552,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3595,45 +3570,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R30" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,12 +3652,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3692,45 +3682,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R31" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,7 +3766,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3776,6 +3775,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034391</v>
+        <v>129034359</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441701</v>
+        <v>441605</v>
       </c>
       <c r="R33" t="n">
-        <v>6780246</v>
+        <v>6780149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034359</v>
+        <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441605</v>
+        <v>441701</v>
       </c>
       <c r="R34" t="n">
-        <v>6780149</v>
+        <v>6780246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034357</v>
+        <v>129034360</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441595</v>
+        <v>441592</v>
       </c>
       <c r="R44" t="n">
-        <v>6780107</v>
+        <v>6780185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129034360</v>
+        <v>129034357</v>
       </c>
       <c r="B45" t="n">
         <v>57724</v>
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441592</v>
+        <v>441595</v>
       </c>
       <c r="R45" t="n">
-        <v>6780185</v>
+        <v>6780107</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -884,45 +884,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034383</v>
+        <v>129034372</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441603</v>
+        <v>441713</v>
       </c>
       <c r="R4" t="n">
-        <v>6780143</v>
+        <v>6780359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +966,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R5" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1078,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,54 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034372</v>
+        <v>129034347</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441713</v>
+        <v>441619</v>
       </c>
       <c r="R6" t="n">
-        <v>6780359</v>
+        <v>6780174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,18 +1181,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,54 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034367</v>
+        <v>129034383</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441649</v>
+        <v>441603</v>
       </c>
       <c r="R7" t="n">
-        <v>6780285</v>
+        <v>6780143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,18 +1278,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034347</v>
+        <v>129034390</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441619</v>
+        <v>441693</v>
       </c>
       <c r="R8" t="n">
-        <v>6780174</v>
+        <v>6780262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,54 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034365</v>
+        <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441629</v>
+        <v>441684</v>
       </c>
       <c r="R12" t="n">
-        <v>6780255</v>
+        <v>6780236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 20 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1789,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034371</v>
+        <v>129034365</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441664</v>
+        <v>441629</v>
       </c>
       <c r="R13" t="n">
-        <v>6780325</v>
+        <v>6780255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,45 +1919,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034392</v>
+        <v>129034371</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441684</v>
+        <v>441664</v>
       </c>
       <c r="R14" t="n">
-        <v>6780236</v>
+        <v>6780325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 20 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,6 +2012,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,49 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B16" t="n">
-        <v>91561</v>
+        <v>56917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R16" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,7 +2212,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2235,45 +2230,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B17" t="n">
-        <v>56917</v>
+        <v>91561</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R17" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,6 +2318,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2952,45 +2952,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034376</v>
+        <v>129034375</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441689</v>
+        <v>441625</v>
       </c>
       <c r="R24" t="n">
-        <v>6780316</v>
+        <v>6780181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,6 +3032,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,7 +3064,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034375</v>
+        <v>129034364</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3094,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441625</v>
+        <v>441595</v>
       </c>
       <c r="R25" t="n">
-        <v>6780181</v>
+        <v>6780188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,54 +3176,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034364</v>
+        <v>129034376</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441595</v>
+        <v>441689</v>
       </c>
       <c r="R26" t="n">
-        <v>6780188</v>
+        <v>6780316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,11 +3247,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3371,45 +3371,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034385</v>
+        <v>129034374</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441619</v>
+        <v>441642</v>
       </c>
       <c r="R28" t="n">
-        <v>6780221</v>
+        <v>6780164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,12 +3453,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3468,45 +3483,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034394</v>
+        <v>129034368</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441672</v>
+        <v>441643</v>
       </c>
       <c r="R29" t="n">
-        <v>6780172</v>
+        <v>6780310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,7 +3567,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 10 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3552,6 +3576,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,54 +3595,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034374</v>
+        <v>129034385</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441642</v>
+        <v>441619</v>
       </c>
       <c r="R30" t="n">
-        <v>6780164</v>
+        <v>6780221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,18 +3668,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3682,54 +3692,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034368</v>
+        <v>129034394</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441643</v>
+        <v>441672</v>
       </c>
       <c r="R31" t="n">
-        <v>6780310</v>
+        <v>6780172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3767,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 10 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3775,7 +3776,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034366</v>
+        <v>129034393</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441640</v>
+        <v>441682</v>
       </c>
       <c r="R2" t="n">
-        <v>6780256</v>
+        <v>6780151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,18 +748,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034393</v>
+        <v>129034366</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441682</v>
+        <v>441640</v>
       </c>
       <c r="R3" t="n">
-        <v>6780151</v>
+        <v>6780256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,54 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034372</v>
+        <v>129034347</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441713</v>
+        <v>441619</v>
       </c>
       <c r="R4" t="n">
-        <v>6780359</v>
+        <v>6780174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,18 +957,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,54 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034367</v>
+        <v>129034390</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441649</v>
+        <v>441693</v>
       </c>
       <c r="R5" t="n">
-        <v>6780285</v>
+        <v>6780262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,18 +1054,12 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129034347</v>
+        <v>129034383</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441619</v>
+        <v>441603</v>
       </c>
       <c r="R6" t="n">
-        <v>6780174</v>
+        <v>6780143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,45 +1175,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129034383</v>
+        <v>129034372</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441603</v>
+        <v>441713</v>
       </c>
       <c r="R7" t="n">
-        <v>6780143</v>
+        <v>6780359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1257,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,45 +1287,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129034390</v>
+        <v>129034367</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441693</v>
+        <v>441649</v>
       </c>
       <c r="R8" t="n">
-        <v>6780262</v>
+        <v>6780285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1369,18 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>129034382</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129034348</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>129034392</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129034386</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,45 +2128,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034351</v>
+        <v>129034355</v>
       </c>
       <c r="B16" t="n">
-        <v>56917</v>
+        <v>91564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441601</v>
+        <v>441612</v>
       </c>
       <c r="R16" t="n">
-        <v>6780177</v>
+        <v>6780106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En större och en mindre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,6 +2216,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2230,49 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034355</v>
+        <v>129034351</v>
       </c>
       <c r="B17" t="n">
-        <v>91561</v>
+        <v>56917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441612</v>
+        <v>441601</v>
       </c>
       <c r="R17" t="n">
-        <v>6780106</v>
+        <v>6780177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En större och en mindre</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,7 +2319,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>129034346</v>
       </c>
       <c r="B18" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129034387</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>129034397</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034352</v>
+        <v>129034373</v>
       </c>
       <c r="B22" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,34 +2749,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441684</v>
+        <v>441691</v>
       </c>
       <c r="R22" t="n">
-        <v>6780293</v>
+        <v>6780347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,7 +2822,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,6 +2831,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2840,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034373</v>
+        <v>129034352</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,43 +2861,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441691</v>
+        <v>441684</v>
       </c>
       <c r="R23" t="n">
-        <v>6780347</v>
+        <v>6780293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2925,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,7 +2934,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,54 +2952,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034375</v>
+        <v>129034376</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>188</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Långt broktagel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria tenuis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441625</v>
+        <v>441689</v>
       </c>
       <c r="R24" t="n">
-        <v>6780181</v>
+        <v>6780316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3064,7 +3050,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034364</v>
+        <v>129034375</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3108,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441595</v>
+        <v>441625</v>
       </c>
       <c r="R25" t="n">
-        <v>6780188</v>
+        <v>6780181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,45 +3162,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034376</v>
+        <v>129034364</v>
       </c>
       <c r="B26" t="n">
-        <v>79077</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>188</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Långt broktagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria tenuis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dahl) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dysberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441689</v>
+        <v>441595</v>
       </c>
       <c r="R26" t="n">
-        <v>6780316</v>
+        <v>6780188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,6 +3242,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3277,7 +3277,7 @@
         <v>129034384</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>129034385</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>129034394</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129034354</v>
       </c>
       <c r="B32" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>129034391</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>129034389</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034395</v>
+        <v>129034349</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441620</v>
+        <v>441687</v>
       </c>
       <c r="R36" t="n">
-        <v>6780175</v>
+        <v>6780170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie om 30 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4302,7 +4302,7 @@
         <v>129034388</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034349</v>
+        <v>129034395</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4412,21 +4412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441687</v>
+        <v>441620</v>
       </c>
       <c r="R38" t="n">
-        <v>6780170</v>
+        <v>6780175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Rikligt i en radie om 30 m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4506,7 +4506,7 @@
         <v>129034396</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 39762-2025 artfynd.xlsx
+++ b/artfynd/A 39762-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034376</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034355</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034382</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034383</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034385</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034386</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034387</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034389</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034390</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034391</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2255,6 +2335,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034392</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2352,6 +2437,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034393</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034394</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2556,6 +2651,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034395</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2658,6 +2758,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034396</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2755,6 +2860,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034397</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2852,6 +2962,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034348</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,6 +3072,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034357</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3062,6 +3182,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034358</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3164,6 +3289,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034359</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3269,6 +3399,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034360</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3374,6 +3509,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034361</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3479,6 +3619,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034362</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3584,6 +3729,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034363</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3686,6 +3836,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034349</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3788,6 +3943,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034351</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3890,6 +4050,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034352</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4000,6 +4165,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034353</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4110,6 +4280,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034377</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4222,6 +4397,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034364</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4334,6 +4514,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034365</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034366</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4558,6 +4748,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034367</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4670,6 +4865,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034368</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4782,6 +4982,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034370</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4894,6 +5099,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034371</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5006,6 +5216,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034372</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5118,6 +5333,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034373</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5230,6 +5450,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034374</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5342,8 +5567,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034375</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>